--- a/testdata/TestData.xlsx
+++ b/testdata/TestData.xlsx
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/applemacbookpro/Documents/SeleniumGuideMukesh/HybridFrameworkSep2022/testdata/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{15271FCB-56A6-FC44-8E7E-5C69EBD96367}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{38102D34-A032-F04F-8410-F92EFAAC6C25}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="7000" yWindow="5460" windowWidth="24720" windowHeight="15460" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="6620" yWindow="4940" windowWidth="24720" windowHeight="15460" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Login" sheetId="1" r:id="rId1"/>
     <sheet name="userdetails" sheetId="2" r:id="rId2"/>
     <sheet name="checkuser" sheetId="3" r:id="rId3"/>
-    <sheet name="Sheet3" sheetId="4" r:id="rId4"/>
+    <sheet name="AdminSearch" sheetId="4" r:id="rId4"/>
     <sheet name="Sheet4" sheetId="5" r:id="rId5"/>
     <sheet name="Sheet5" sheetId="6" r:id="rId6"/>
     <sheet name="Sheet6" sheetId="7" r:id="rId7"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="16">
   <si>
     <t>Username</t>
   </si>
@@ -61,13 +61,31 @@
   </si>
   <si>
     <t>SnehaB@gmail.com</t>
+  </si>
+  <si>
+    <t>UserName</t>
+  </si>
+  <si>
+    <t>UserRole</t>
+  </si>
+  <si>
+    <t>EmployeeName</t>
+  </si>
+  <si>
+    <t>Status</t>
+  </si>
+  <si>
+    <t>Enabled</t>
+  </si>
+  <si>
+    <t>Minh Nguyen</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -85,6 +103,14 @@
     </font>
     <font>
       <sz val="15"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
@@ -127,11 +153,12 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -462,7 +489,7 @@
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A2" t="s">
+      <c r="A2" s="1" t="s">
         <v>7</v>
       </c>
       <c r="B2" s="1" t="s">
@@ -548,9 +575,59 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1"/>
+  <dimension ref="A1:D5"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
-  <sheetData/>
+  <cols>
+    <col min="3" max="3" width="14.1640625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="B1" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C1" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="D1" s="4" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A2" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A3" s="1"/>
+      <c r="B3" s="1"/>
+      <c r="C3" s="1"/>
+      <c r="D3" s="1"/>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A4" s="1"/>
+      <c r="B4" s="1"/>
+      <c r="C4" s="1"/>
+      <c r="D4" s="1"/>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A5" s="1"/>
+      <c r="B5" s="1"/>
+      <c r="C5" s="1"/>
+      <c r="D5" s="1"/>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
